--- a/data/trans_orig/P6709-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P6709-Edad-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tiene influencia sobre el orden en el que realizan las tareas en 2012</t>
+          <t>Población según si tiene influencia sobre el orden en el que realizan las tareas en 2012 (tasa de respuesta: 98,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>6181</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21361</t>
+          <t>22496</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5399</t>
+          <t>5202</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17351</t>
+          <t>17440</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14317</t>
+          <t>14300</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34223</t>
+          <t>33135</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>5383</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18575</t>
+          <t>18031</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>998</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9846</t>
+          <t>8951</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8423</t>
+          <t>8285</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23912</t>
+          <t>23093</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,69%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9940</t>
+          <t>10015</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24268</t>
+          <t>25200</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12770</t>
+          <t>12868</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27556</t>
+          <t>28015</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26497</t>
+          <t>26193</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>47558</t>
+          <t>47196</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>27,97%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10585</t>
+          <t>10548</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25077</t>
+          <t>25958</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12125</t>
+          <t>12232</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26909</t>
+          <t>27077</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26580</t>
+          <t>26625</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47053</t>
+          <t>46224</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,39%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17801</t>
+          <t>16891</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35100</t>
+          <t>34471</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>25521</t>
+          <t>24953</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43084</t>
+          <t>42949</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>46235</t>
+          <t>47143</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>72010</t>
+          <t>73218</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>43,39%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22984</t>
+          <t>22700</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47444</t>
+          <t>45927</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19815</t>
+          <t>19639</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41811</t>
+          <t>39730</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47793</t>
+          <t>45560</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80930</t>
+          <t>79182</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,06%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18431</t>
+          <t>18146</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38896</t>
+          <t>38627</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14816</t>
+          <t>13436</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35835</t>
+          <t>33591</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>36980</t>
+          <t>36887</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>67502</t>
+          <t>65836</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>76519</t>
+          <t>77437</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>110999</t>
+          <t>110295</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>47693</t>
+          <t>48556</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>76985</t>
+          <t>77358</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>133764</t>
+          <t>133794</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>179097</t>
+          <t>178977</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,25%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76772</t>
+          <t>75747</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>108042</t>
+          <t>107669</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55652</t>
+          <t>55083</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83401</t>
+          <t>85262</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>139966</t>
+          <t>143076</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>182875</t>
+          <t>189188</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>28,8%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>117043</t>
+          <t>118221</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>155568</t>
+          <t>155973</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75298</t>
+          <t>76290</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>107372</t>
+          <t>106878</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>202518</t>
+          <t>201933</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>253186</t>
+          <t>251500</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,29%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18995</t>
+          <t>18887</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42204</t>
+          <t>41075</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14729</t>
+          <t>14926</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33090</t>
+          <t>32778</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38313</t>
+          <t>38369</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>67464</t>
+          <t>68678</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21148</t>
+          <t>22377</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45062</t>
+          <t>44819</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17104</t>
+          <t>16201</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36875</t>
+          <t>37405</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>42883</t>
+          <t>43976</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>73819</t>
+          <t>73028</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>72565</t>
+          <t>72817</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>104709</t>
+          <t>106216</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>46711</t>
+          <t>46180</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>74807</t>
+          <t>73777</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>128061</t>
+          <t>126790</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>169061</t>
+          <t>169140</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,89%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>100254</t>
+          <t>98998</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>136848</t>
+          <t>135114</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47055</t>
+          <t>47212</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>74858</t>
+          <t>76032</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>154874</t>
+          <t>155258</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>201946</t>
+          <t>200813</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,36%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>137350</t>
+          <t>136577</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>177892</t>
+          <t>177716</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>101551</t>
+          <t>98524</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>134996</t>
+          <t>132580</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>249034</t>
+          <t>247203</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>298874</t>
+          <t>301952</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>42,64%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11143</t>
+          <t>11088</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27732</t>
+          <t>27839</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15190</t>
+          <t>16404</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36063</t>
+          <t>37020</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30328</t>
+          <t>30301</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>57580</t>
+          <t>56668</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14960</t>
+          <t>14620</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>35784</t>
+          <t>33927</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7563</t>
+          <t>7606</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>24341</t>
+          <t>23142</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>26536</t>
+          <t>26672</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>51508</t>
+          <t>51491</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>52623</t>
+          <t>51637</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>84644</t>
+          <t>84897</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>28613</t>
+          <t>28539</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>56014</t>
+          <t>54873</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>88307</t>
+          <t>89277</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>129883</t>
+          <t>131724</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,33%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>79601</t>
+          <t>78488</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>116100</t>
+          <t>115776</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>33081</t>
+          <t>33573</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>58838</t>
+          <t>59225</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>118565</t>
+          <t>119300</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>163350</t>
+          <t>162373</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,53%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>142067</t>
+          <t>141090</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>181965</t>
+          <t>183745</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>82674</t>
+          <t>82541</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>113509</t>
+          <t>114095</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>233484</t>
+          <t>238258</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>287278</t>
+          <t>289268</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>49,04%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>2093</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11880</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10857</t>
+          <t>10012</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4289</t>
+          <t>4772</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>17184</t>
+          <t>17569</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2147</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13165</t>
+          <t>11940</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8216</t>
+          <t>6549</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4223</t>
+          <t>3329</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>16742</t>
+          <t>15912</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>21019</t>
+          <t>20704</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>41709</t>
+          <t>41291</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7416</t>
+          <t>8114</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>20894</t>
+          <t>22317</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>31946</t>
+          <t>32491</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>55993</t>
+          <t>56935</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>25,31%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>24009</t>
+          <t>24448</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>44883</t>
+          <t>46772</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>9424</t>
+          <t>9646</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>23954</t>
+          <t>24231</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>38168</t>
+          <t>37277</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>64018</t>
+          <t>63934</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,42%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>67883</t>
+          <t>67706</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>92724</t>
+          <t>93233</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>23840</t>
+          <t>24185</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>40803</t>
+          <t>41305</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>97092</t>
+          <t>98127</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>128255</t>
+          <t>128931</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>57,31%</t>
         </is>
       </c>
     </row>
@@ -4141,97 +4141,97 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>1339</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>1260</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>1546</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4254,97 +4254,97 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>1339</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="R35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>1260</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>1546</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>79594</t>
+          <t>78148</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>120522</t>
+          <t>118399</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>75015</t>
+          <t>71686</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>110431</t>
+          <t>110813</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>160064</t>
+          <t>163329</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>217943</t>
+          <t>219252</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>80968</t>
+          <t>81554</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>121206</t>
+          <t>119531</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>52296</t>
+          <t>51743</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>88417</t>
+          <t>88337</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>142534</t>
+          <t>141974</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>194745</t>
+          <t>195651</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>265252</t>
+          <t>264048</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>328253</t>
+          <t>329847</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>167984</t>
+          <t>169162</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>223492</t>
+          <t>223138</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>452047</t>
+          <t>449692</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>536118</t>
+          <t>533137</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>324434</t>
+          <t>323291</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>393412</t>
+          <t>393347</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>184042</t>
+          <t>186191</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>241139</t>
+          <t>237077</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>523479</t>
+          <t>525727</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>610284</t>
+          <t>606867</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,78%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>526027</t>
+          <t>526995</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>603274</t>
+          <t>603724</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>341515</t>
+          <t>343983</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>405039</t>
+          <t>405738</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>890026</t>
+          <t>893456</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>988726</t>
+          <t>989120</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>42,01%</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6227,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tiene influencia sobre el orden en el que realizan las tareas en 2016</t>
+          <t>Población según si tiene influencia sobre el orden en el que realizan las tareas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7585</t>
+          <t>8264</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20545</t>
+          <t>22414</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2422</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12001</t>
+          <t>12668</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12714</t>
+          <t>13163</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29437</t>
+          <t>30789</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5034</t>
+          <t>4962</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17710</t>
+          <t>16948</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6997</t>
+          <t>6375</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20941</t>
+          <t>20006</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14598</t>
+          <t>13717</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31936</t>
+          <t>32701</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20717</t>
+          <t>19607</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38347</t>
+          <t>37440</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23674</t>
+          <t>23440</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>41720</t>
+          <t>41669</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>48460</t>
+          <t>48369</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>73242</t>
+          <t>72936</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,66%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8663</t>
+          <t>9016</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23396</t>
+          <t>22703</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9455</t>
+          <t>8852</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23401</t>
+          <t>22410</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21348</t>
+          <t>20929</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40395</t>
+          <t>41204</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>24,1%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6804</t>
+          <t>7132</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19811</t>
+          <t>19579</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17664</t>
+          <t>18084</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>34623</t>
+          <t>35122</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>28563</t>
+          <t>29414</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>50550</t>
+          <t>51974</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>30,4%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31328</t>
+          <t>30097</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55825</t>
+          <t>55926</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17295</t>
+          <t>17986</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37668</t>
+          <t>37084</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55284</t>
+          <t>55439</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86614</t>
+          <t>86306</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43356</t>
+          <t>42799</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>70593</t>
+          <t>71915</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27635</t>
+          <t>27955</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49030</t>
+          <t>49618</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>76730</t>
+          <t>76756</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>111430</t>
+          <t>111460</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,04%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>76512</t>
+          <t>76858</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>108601</t>
+          <t>110993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>66477</t>
+          <t>66283</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>95497</t>
+          <t>95731</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>150758</t>
+          <t>153505</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>196727</t>
+          <t>198279</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>32,09%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59042</t>
+          <t>60164</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89649</t>
+          <t>89729</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58980</t>
+          <t>58650</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>86797</t>
+          <t>86695</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>126744</t>
+          <t>126695</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>168766</t>
+          <t>166689</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>26,98%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>65468</t>
+          <t>63327</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>97943</t>
+          <t>94965</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45338</t>
+          <t>45132</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71134</t>
+          <t>71777</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>118173</t>
+          <t>117745</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>157637</t>
+          <t>159433</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,8%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33244</t>
+          <t>32758</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58527</t>
+          <t>58703</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32041</t>
+          <t>30326</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54770</t>
+          <t>54097</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>69874</t>
+          <t>70894</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>105157</t>
+          <t>105775</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,61%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>42458</t>
+          <t>43262</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>71921</t>
+          <t>71409</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36762</t>
+          <t>36204</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>59762</t>
+          <t>61046</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>87575</t>
+          <t>86957</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>124022</t>
+          <t>123506</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,9%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>103080</t>
+          <t>104215</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>142347</t>
+          <t>142980</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>55346</t>
+          <t>53065</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>82119</t>
+          <t>81922</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>166965</t>
+          <t>165661</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>215833</t>
+          <t>213270</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,45%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>94072</t>
+          <t>93864</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>131724</t>
+          <t>133085</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>60211</t>
+          <t>60045</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>89452</t>
+          <t>88866</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>158895</t>
+          <t>161684</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>210188</t>
+          <t>212821</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,39%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>105094</t>
+          <t>104634</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>143647</t>
+          <t>142374</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>72560</t>
+          <t>72337</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>103189</t>
+          <t>105033</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>187679</t>
+          <t>187655</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>237206</t>
+          <t>239108</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,77%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25853</t>
+          <t>25334</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50488</t>
+          <t>50159</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16320</t>
+          <t>16296</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36584</t>
+          <t>35652</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>46417</t>
+          <t>46910</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>78694</t>
+          <t>78032</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,77%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>33865</t>
+          <t>34239</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>62099</t>
+          <t>62204</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>22755</t>
+          <t>24143</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>46768</t>
+          <t>47323</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>62833</t>
+          <t>63484</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>100301</t>
+          <t>96270</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>73913</t>
+          <t>75274</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>108838</t>
+          <t>109975</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>49960</t>
+          <t>50186</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>78990</t>
+          <t>76900</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>131646</t>
+          <t>134546</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>174019</t>
+          <t>175993</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,81%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>71695</t>
+          <t>71341</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>107068</t>
+          <t>105285</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>39206</t>
+          <t>39947</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>65089</t>
+          <t>64845</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>117698</t>
+          <t>120329</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>162335</t>
+          <t>162592</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,62%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>87760</t>
+          <t>85630</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>125291</t>
+          <t>123065</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>56206</t>
+          <t>56391</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>86056</t>
+          <t>86236</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>153857</t>
+          <t>153942</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>199683</t>
+          <t>200351</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,8%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9094</t>
+          <t>9901</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26089</t>
+          <t>26722</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>18687</t>
+          <t>18111</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>17572</t>
+          <t>17965</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>37708</t>
+          <t>39433</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,52%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11256</t>
+          <t>11144</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>28077</t>
+          <t>28275</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>12288</t>
+          <t>12444</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>29106</t>
+          <t>29261</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>27293</t>
+          <t>27414</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>51069</t>
+          <t>52264</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,24%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>31210</t>
+          <t>29758</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>55871</t>
+          <t>54859</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13593</t>
+          <t>13773</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>31342</t>
+          <t>30380</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>48398</t>
+          <t>48206</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>77177</t>
+          <t>79552</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>29,29%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>20432</t>
+          <t>21018</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>41995</t>
+          <t>41802</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>14643</t>
+          <t>15305</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>33433</t>
+          <t>33105</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>40712</t>
+          <t>41776</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>68355</t>
+          <t>68312</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,15%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>46836</t>
+          <t>46992</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>72538</t>
+          <t>72809</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>21579</t>
+          <t>22055</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>41748</t>
+          <t>42033</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>73683</t>
+          <t>74794</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>107006</t>
+          <t>104833</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>38,6%</t>
         </is>
       </c>
     </row>
@@ -9832,97 +9832,97 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>4027</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>19,65%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>77,59%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>1020</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>4248</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>19,65%</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>4186</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>9,83%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>81,84%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>1020</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>4251</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>9,83%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,32%</t>
         </is>
       </c>
     </row>
@@ -9945,97 +9945,97 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="R35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>1773</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10058,97 +10058,97 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>1183</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>4357</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>22,79%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>83,94%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="R36" s="2" t="inlineStr">
         <is>
           <t>1183</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="S36" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>4269</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>22,79%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>4605</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>11,39%</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>82,26%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>1183</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>5584</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>11,39%</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>44,36%</t>
         </is>
       </c>
     </row>
@@ -10206,62 +10206,62 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>2075</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>6167</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>19,99%</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>2075</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>5365</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>19,99%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>59,41%</t>
         </is>
       </c>
     </row>
@@ -10319,7 +10319,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>833</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2204</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>9269</t>
+          <t>9299</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,57%</t>
         </is>
       </c>
     </row>
@@ -10514,97 +10514,97 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10627,97 +10627,97 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10740,97 +10740,97 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10853,97 +10853,97 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
           <t>795</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10966,97 +10966,97 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>130281</t>
+          <t>130460</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>181842</t>
+          <t>177202</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>90577</t>
+          <t>93070</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>129420</t>
+          <t>131500</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>235043</t>
+          <t>233025</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>294609</t>
+          <t>299007</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -11309,12 +11309,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>162647</t>
+          <t>162868</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>214470</t>
+          <t>216988</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -11324,12 +11324,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11344,12 +11344,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>126839</t>
+          <t>129095</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>170905</t>
+          <t>176792</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11359,12 +11359,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>301717</t>
+          <t>303796</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>373570</t>
+          <t>373233</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11394,12 +11394,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>
@@ -11422,12 +11422,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>343032</t>
+          <t>342700</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>412705</t>
+          <t>411205</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -11437,12 +11437,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -11457,12 +11457,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>238166</t>
+          <t>238857</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>290770</t>
+          <t>294122</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -11492,12 +11492,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>602069</t>
+          <t>596678</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>691261</t>
+          <t>686570</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -11507,12 +11507,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,92%</t>
         </is>
       </c>
     </row>
@@ -11535,12 +11535,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>285910</t>
+          <t>290987</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>352403</t>
+          <t>353453</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -11550,12 +11550,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -11570,12 +11570,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>209617</t>
+          <t>210796</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>261602</t>
+          <t>266907</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -11585,12 +11585,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -11605,12 +11605,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>515673</t>
+          <t>518572</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>597537</t>
+          <t>603207</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -11620,12 +11620,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -11648,12 +11648,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>350384</t>
+          <t>348712</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>419491</t>
+          <t>421042</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -11663,12 +11663,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -11683,12 +11683,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>250980</t>
+          <t>247956</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>306705</t>
+          <t>304775</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -11698,12 +11698,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -11718,12 +11718,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>615537</t>
+          <t>613060</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>705161</t>
+          <t>704282</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -11733,12 +11733,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,64%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6709-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P6709-Edad-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6181</t>
+          <t>6067</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22496</t>
+          <t>21348</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5202</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17440</t>
+          <t>17119</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14300</t>
+          <t>14272</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33135</t>
+          <t>34258</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>20,3%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5383</t>
+          <t>5605</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18031</t>
+          <t>19079</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>999</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8951</t>
+          <t>9468</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8285</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23093</t>
+          <t>23249</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,78%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10015</t>
+          <t>10051</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25200</t>
+          <t>24465</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12868</t>
+          <t>13790</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28015</t>
+          <t>28550</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26193</t>
+          <t>26829</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>47196</t>
+          <t>48201</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10548</t>
+          <t>10181</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25958</t>
+          <t>25176</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12232</t>
+          <t>12664</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27077</t>
+          <t>27422</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26625</t>
+          <t>26327</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46224</t>
+          <t>47615</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>28,22%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16891</t>
+          <t>17191</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>34471</t>
+          <t>34815</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24953</t>
+          <t>25009</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>42949</t>
+          <t>43484</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>47143</t>
+          <t>47969</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>73218</t>
+          <t>73018</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,27%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22700</t>
+          <t>22384</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45927</t>
+          <t>46665</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19639</t>
+          <t>19418</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39730</t>
+          <t>40972</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45560</t>
+          <t>47905</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79182</t>
+          <t>78766</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18146</t>
+          <t>18152</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38627</t>
+          <t>39019</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13436</t>
+          <t>13770</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33591</t>
+          <t>34903</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>36887</t>
+          <t>36201</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>65836</t>
+          <t>66598</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>77437</t>
+          <t>77386</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>110295</t>
+          <t>112954</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>48556</t>
+          <t>49857</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>77358</t>
+          <t>76967</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>133794</t>
+          <t>135071</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>178977</t>
+          <t>178703</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,21%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75747</t>
+          <t>77990</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>107669</t>
+          <t>109782</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55083</t>
+          <t>56022</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85262</t>
+          <t>85069</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>143076</t>
+          <t>142914</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>189188</t>
+          <t>185767</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,28%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>118221</t>
+          <t>117194</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>155973</t>
+          <t>155226</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>76290</t>
+          <t>75687</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>106878</t>
+          <t>108580</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>201933</t>
+          <t>204182</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>251500</t>
+          <t>252678</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,47%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18887</t>
+          <t>19876</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41075</t>
+          <t>42571</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14926</t>
+          <t>14800</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32778</t>
+          <t>33315</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38369</t>
+          <t>37492</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>68678</t>
+          <t>66261</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22377</t>
+          <t>21710</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44819</t>
+          <t>44622</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16201</t>
+          <t>16751</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37405</t>
+          <t>37920</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>43976</t>
+          <t>42952</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>73028</t>
+          <t>72215</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>72817</t>
+          <t>74295</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>106216</t>
+          <t>106788</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>46180</t>
+          <t>45420</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>73777</t>
+          <t>74011</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>126790</t>
+          <t>124721</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>169140</t>
+          <t>167029</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,59%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>98998</t>
+          <t>99771</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>135114</t>
+          <t>137057</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47212</t>
+          <t>46307</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>76032</t>
+          <t>75781</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>155258</t>
+          <t>155336</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>200813</t>
+          <t>201675</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,48%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>136577</t>
+          <t>138097</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>177716</t>
+          <t>179577</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>98524</t>
+          <t>100177</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>132580</t>
+          <t>135018</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>247203</t>
+          <t>250569</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>301952</t>
+          <t>303679</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,89%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11088</t>
+          <t>11118</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27839</t>
+          <t>29332</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16404</t>
+          <t>15002</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>37020</t>
+          <t>36815</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30301</t>
+          <t>31525</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56668</t>
+          <t>57179</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14620</t>
+          <t>15306</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>33927</t>
+          <t>35477</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7606</t>
+          <t>7589</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>23142</t>
+          <t>23354</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>26672</t>
+          <t>25629</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>51491</t>
+          <t>51401</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>51637</t>
+          <t>52485</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>84897</t>
+          <t>84427</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>28539</t>
+          <t>30006</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>54873</t>
+          <t>57109</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>89277</t>
+          <t>91335</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>131724</t>
+          <t>131047</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,22%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>78488</t>
+          <t>78452</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>115776</t>
+          <t>115667</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>33573</t>
+          <t>32567</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>59225</t>
+          <t>56871</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>119300</t>
+          <t>117966</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>162373</t>
+          <t>166126</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>28,17%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>141090</t>
+          <t>141262</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>183745</t>
+          <t>183936</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>82541</t>
+          <t>81615</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>114095</t>
+          <t>115767</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>238258</t>
+          <t>231825</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>289268</t>
+          <t>284178</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>48,18%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2093</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>11590</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10012</t>
+          <t>10092</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>4817</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>17569</t>
+          <t>17979</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>2172</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11940</t>
+          <t>13111</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6549</t>
+          <t>6471</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3329</t>
+          <t>4180</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15912</t>
+          <t>16129</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20704</t>
+          <t>21276</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>41291</t>
+          <t>40714</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8114</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>22317</t>
+          <t>22110</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>32491</t>
+          <t>32859</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>56935</t>
+          <t>56120</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>24,94%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>24448</t>
+          <t>24257</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>46772</t>
+          <t>45872</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>9646</t>
+          <t>9504</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>24231</t>
+          <t>23873</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>37277</t>
+          <t>37511</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>63934</t>
+          <t>62661</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>27,85%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>67706</t>
+          <t>68043</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>93233</t>
+          <t>92266</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>24185</t>
+          <t>23993</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>41305</t>
+          <t>41068</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>98127</t>
+          <t>98003</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>128931</t>
+          <t>128053</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>56,92%</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>68,29%</t>
         </is>
       </c>
     </row>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4822</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>66,13%</t>
         </is>
       </c>
     </row>
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>985</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,82%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>78148</t>
+          <t>78124</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>118399</t>
+          <t>120454</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>71686</t>
+          <t>72877</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>110813</t>
+          <t>110186</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>163329</t>
+          <t>160822</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>219252</t>
+          <t>217210</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>81554</t>
+          <t>79240</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>119531</t>
+          <t>120294</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>51743</t>
+          <t>53263</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>88337</t>
+          <t>86770</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>141974</t>
+          <t>146056</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>195651</t>
+          <t>197377</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>264048</t>
+          <t>266200</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>329847</t>
+          <t>329156</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>169162</t>
+          <t>170709</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>223138</t>
+          <t>224412</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>449692</t>
+          <t>450901</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>533137</t>
+          <t>535863</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,76%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>323291</t>
+          <t>323562</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>393347</t>
+          <t>389976</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>186191</t>
+          <t>186581</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>237077</t>
+          <t>236972</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>525727</t>
+          <t>524110</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>606867</t>
+          <t>609941</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,91%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>526995</t>
+          <t>527795</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>603724</t>
+          <t>605674</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>343983</t>
+          <t>340818</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>405738</t>
+          <t>404481</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>893456</t>
+          <t>889055</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>989120</t>
+          <t>987087</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>41,93%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8264</t>
+          <t>7495</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22414</t>
+          <t>21437</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2422</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12668</t>
+          <t>12162</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13163</t>
+          <t>12477</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30789</t>
+          <t>29458</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,23%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4962</t>
+          <t>4108</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16948</t>
+          <t>16337</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6375</t>
+          <t>6714</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20006</t>
+          <t>21178</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13717</t>
+          <t>13877</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32701</t>
+          <t>31829</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>18,62%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19607</t>
+          <t>19678</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37440</t>
+          <t>37201</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23440</t>
+          <t>22637</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>41669</t>
+          <t>41236</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>48369</t>
+          <t>47275</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>72936</t>
+          <t>72765</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,56%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9016</t>
+          <t>8998</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22703</t>
+          <t>22761</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8852</t>
+          <t>8819</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22410</t>
+          <t>23315</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20929</t>
+          <t>20999</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41204</t>
+          <t>41263</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,14%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>6545</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19579</t>
+          <t>20135</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18084</t>
+          <t>17969</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35122</t>
+          <t>35547</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>29414</t>
+          <t>29312</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>51974</t>
+          <t>50737</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>29,68%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30097</t>
+          <t>30119</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55926</t>
+          <t>55161</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17986</t>
+          <t>17373</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37084</t>
+          <t>36666</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55439</t>
+          <t>54109</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86306</t>
+          <t>87039</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42799</t>
+          <t>42092</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>71915</t>
+          <t>69566</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27955</t>
+          <t>28293</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49618</t>
+          <t>51625</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>76756</t>
+          <t>79557</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>111460</t>
+          <t>113456</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,36%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>76858</t>
+          <t>76799</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>110993</t>
+          <t>109683</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>66283</t>
+          <t>66940</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>95731</t>
+          <t>95357</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>153505</t>
+          <t>152363</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>198279</t>
+          <t>193688</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>31,35%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60164</t>
+          <t>59390</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89729</t>
+          <t>89784</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58650</t>
+          <t>57451</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>86695</t>
+          <t>86505</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>126695</t>
+          <t>125726</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>166689</t>
+          <t>166179</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,89%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63327</t>
+          <t>66490</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>94965</t>
+          <t>97964</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45132</t>
+          <t>46365</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71777</t>
+          <t>72205</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>117745</t>
+          <t>116831</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>159433</t>
+          <t>157267</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32758</t>
+          <t>33519</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58703</t>
+          <t>59767</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30326</t>
+          <t>30725</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54097</t>
+          <t>55919</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>70894</t>
+          <t>70313</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>105775</t>
+          <t>104371</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43262</t>
+          <t>44120</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>71409</t>
+          <t>72955</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36204</t>
+          <t>36586</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>61046</t>
+          <t>60973</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>86957</t>
+          <t>86212</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>123506</t>
+          <t>122020</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,7%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>104215</t>
+          <t>102723</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>142980</t>
+          <t>143784</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>53065</t>
+          <t>54713</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>81922</t>
+          <t>83669</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>165661</t>
+          <t>166297</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>213270</t>
+          <t>214668</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,63%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>93864</t>
+          <t>93320</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>133085</t>
+          <t>129839</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>60045</t>
+          <t>59291</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>88866</t>
+          <t>89906</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>161684</t>
+          <t>159612</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>212821</t>
+          <t>209161</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>26,92%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>104634</t>
+          <t>105214</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>142374</t>
+          <t>145109</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>72337</t>
+          <t>73220</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>105033</t>
+          <t>103866</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>187655</t>
+          <t>185176</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>239108</t>
+          <t>237240</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,53%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25334</t>
+          <t>24957</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50159</t>
+          <t>48917</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16296</t>
+          <t>16295</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35652</t>
+          <t>35734</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>46910</t>
+          <t>46731</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>78032</t>
+          <t>76917</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>34239</t>
+          <t>34861</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>62204</t>
+          <t>61457</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24143</t>
+          <t>23230</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>47323</t>
+          <t>45650</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>63484</t>
+          <t>63122</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>96270</t>
+          <t>101157</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>75274</t>
+          <t>74069</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>109975</t>
+          <t>109252</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>50186</t>
+          <t>49445</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>76900</t>
+          <t>77031</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>134546</t>
+          <t>130956</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>175993</t>
+          <t>175341</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,7%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>71341</t>
+          <t>70631</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>105285</t>
+          <t>105321</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>39947</t>
+          <t>39713</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>64845</t>
+          <t>66694</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>120329</t>
+          <t>121753</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>162592</t>
+          <t>164919</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>27,0%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>85630</t>
+          <t>88195</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>123065</t>
+          <t>124298</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>56391</t>
+          <t>56864</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>86236</t>
+          <t>85280</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>153942</t>
+          <t>153614</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>200351</t>
+          <t>201149</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,93%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9901</t>
+          <t>9038</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26722</t>
+          <t>26314</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>18111</t>
+          <t>18976</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>17965</t>
+          <t>17062</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>39433</t>
+          <t>38015</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,0%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>11315</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>28275</t>
+          <t>28353</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>12444</t>
+          <t>11845</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>29261</t>
+          <t>28555</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>27414</t>
+          <t>27663</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>52264</t>
+          <t>52184</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,21%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>29758</t>
+          <t>30074</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>54859</t>
+          <t>54459</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13773</t>
+          <t>13425</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>30380</t>
+          <t>30995</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>48206</t>
+          <t>48118</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>79552</t>
+          <t>79414</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,24%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21018</t>
+          <t>20870</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>41802</t>
+          <t>42426</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>15305</t>
+          <t>15534</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>33105</t>
+          <t>33627</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>41776</t>
+          <t>40784</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>68312</t>
+          <t>68809</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,33%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>46992</t>
+          <t>47044</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>72809</t>
+          <t>73240</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>22055</t>
+          <t>22589</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>42033</t>
+          <t>43545</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>74794</t>
+          <t>75436</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>104833</t>
+          <t>108286</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>39,87%</t>
         </is>
       </c>
     </row>
@@ -9872,7 +9872,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4186</t>
+          <t>5143</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>49,54%</t>
         </is>
       </c>
     </row>
@@ -10098,7 +10098,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10133,7 +10133,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4605</t>
+          <t>4591</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>44,22%</t>
         </is>
       </c>
     </row>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4241</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6167</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>52,03%</t>
         </is>
       </c>
     </row>
@@ -10284,7 +10284,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>953</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -10319,7 +10319,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>858</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>2867</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>9299</t>
+          <t>9283</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,42%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>130460</t>
+          <t>130973</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>177202</t>
+          <t>180669</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>93070</t>
+          <t>90551</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>131500</t>
+          <t>130865</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>233025</t>
+          <t>233925</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>299007</t>
+          <t>294801</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -11309,12 +11309,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>162868</t>
+          <t>164250</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>216988</t>
+          <t>215049</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -11324,12 +11324,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11344,12 +11344,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>129095</t>
+          <t>128212</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>176792</t>
+          <t>174676</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11359,12 +11359,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>303796</t>
+          <t>306785</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>373233</t>
+          <t>377115</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11394,12 +11394,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -11422,12 +11422,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>342700</t>
+          <t>341734</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>411205</t>
+          <t>409792</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -11437,12 +11437,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -11457,12 +11457,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>238857</t>
+          <t>236716</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>294122</t>
+          <t>294006</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -11492,12 +11492,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>596678</t>
+          <t>598207</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>686570</t>
+          <t>686104</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -11507,12 +11507,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,9%</t>
         </is>
       </c>
     </row>
@@ -11535,12 +11535,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>290987</t>
+          <t>289668</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>353453</t>
+          <t>351943</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -11550,12 +11550,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -11570,12 +11570,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>210796</t>
+          <t>210784</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>266907</t>
+          <t>264674</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -11605,12 +11605,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>518572</t>
+          <t>514668</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>603207</t>
+          <t>596124</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -11620,12 +11620,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,24%</t>
         </is>
       </c>
     </row>
@@ -11648,12 +11648,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>348712</t>
+          <t>350620</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>421042</t>
+          <t>417421</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -11663,49 +11663,49 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
+          <t>29,35%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>276004</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>249378</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>307040</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>26,61%</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>24,04%</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
           <t>29,6%</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>276004</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>247956</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>304775</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>26,61%</t>
-        </is>
-      </c>
-      <c r="O50" s="2" t="inlineStr">
-        <is>
-          <t>23,91%</t>
-        </is>
-      </c>
-      <c r="P50" s="2" t="inlineStr">
-        <is>
-          <t>29,39%</t>
-        </is>
-      </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
           <t>616</t>
@@ -11718,12 +11718,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>613060</t>
+          <t>613053</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>704282</t>
+          <t>708184</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -11738,7 +11738,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,79%</t>
         </is>
       </c>
     </row>
